--- a/output/yearly_total_coral_cover_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_1_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.278693432631424</v>
+        <v>1.25003621714446</v>
       </c>
       <c r="C3" t="n">
-        <v>4.572290528805719</v>
+        <v>4.609430044457376</v>
       </c>
       <c r="D3" t="n">
-        <v>6.046432033496587</v>
+        <v>6.213289873310375</v>
       </c>
       <c r="E3" t="n">
-        <v>11.89741599493373</v>
+        <v>12.07275613491221</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.436253299608895</v>
+        <v>1.36463416326243</v>
       </c>
       <c r="C4" t="n">
-        <v>4.98444329327718</v>
+        <v>5.071690741739325</v>
       </c>
       <c r="D4" t="n">
-        <v>6.352091360099481</v>
+        <v>6.623570512313348</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77278795298556</v>
+        <v>13.0598954173151</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.644618723726524</v>
+        <v>1.526670896276484</v>
       </c>
       <c r="C5" t="n">
-        <v>5.550331668852996</v>
+        <v>5.661734659085555</v>
       </c>
       <c r="D5" t="n">
-        <v>6.66561424885447</v>
+        <v>7.059443235250279</v>
       </c>
       <c r="E5" t="n">
-        <v>13.86056464143399</v>
+        <v>14.24784879061232</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.882039453130368</v>
+        <v>1.710738983813212</v>
       </c>
       <c r="C6" t="n">
-        <v>6.266210727983007</v>
+        <v>6.39714752470359</v>
       </c>
       <c r="D6" t="n">
-        <v>7.041011963548399</v>
+        <v>7.498702950836869</v>
       </c>
       <c r="E6" t="n">
-        <v>15.18926214466178</v>
+        <v>15.60658945935367</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.167006385979035</v>
+        <v>1.910364060536848</v>
       </c>
       <c r="C7" t="n">
-        <v>7.186370632921173</v>
+        <v>7.295604067845376</v>
       </c>
       <c r="D7" t="n">
-        <v>7.401843648986953</v>
+        <v>7.919219048187372</v>
       </c>
       <c r="E7" t="n">
-        <v>16.75522066788716</v>
+        <v>17.1251871765696</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.386798314152691</v>
+        <v>1.131284224143347</v>
       </c>
       <c r="C8" t="n">
-        <v>4.994404261132808</v>
+        <v>5.030943853070781</v>
       </c>
       <c r="D8" t="n">
-        <v>5.725715456104398</v>
+        <v>6.184224309267178</v>
       </c>
       <c r="E8" t="n">
-        <v>12.1069180313899</v>
+        <v>12.3464523864813</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.762694788272726</v>
+        <v>1.393508851268624</v>
       </c>
       <c r="C9" t="n">
-        <v>6.214958986816447</v>
+        <v>6.22290430521463</v>
       </c>
       <c r="D9" t="n">
-        <v>6.206345531119328</v>
+        <v>6.73624944889241</v>
       </c>
       <c r="E9" t="n">
-        <v>14.1839993062085</v>
+        <v>14.35266260537566</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.160918503422812</v>
+        <v>1.665334522086016</v>
       </c>
       <c r="C10" t="n">
-        <v>7.573688946259984</v>
+        <v>7.591175547608043</v>
       </c>
       <c r="D10" t="n">
-        <v>6.761034816349836</v>
+        <v>7.2898780799112</v>
       </c>
       <c r="E10" t="n">
-        <v>16.49564226603263</v>
+        <v>16.54638814960526</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.556475600202048</v>
+        <v>1.93805791494681</v>
       </c>
       <c r="C11" t="n">
-        <v>8.992145925413505</v>
+        <v>9.119656841277614</v>
       </c>
       <c r="D11" t="n">
-        <v>7.272246046536157</v>
+        <v>7.950153228552725</v>
       </c>
       <c r="E11" t="n">
-        <v>18.82086757215171</v>
+        <v>19.00786798477715</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.960568712289778</v>
+        <v>2.212493965901895</v>
       </c>
       <c r="C12" t="n">
-        <v>10.438458832877</v>
+        <v>10.70911728355624</v>
       </c>
       <c r="D12" t="n">
-        <v>7.785898078042535</v>
+        <v>8.514975260105972</v>
       </c>
       <c r="E12" t="n">
-        <v>21.18492562320931</v>
+        <v>21.43658650956411</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.352275559729185</v>
+        <v>2.47154541766642</v>
       </c>
       <c r="C13" t="n">
-        <v>11.94599970678671</v>
+        <v>12.3523616902932</v>
       </c>
       <c r="D13" t="n">
-        <v>8.229911029811078</v>
+        <v>9.063506451472721</v>
       </c>
       <c r="E13" t="n">
-        <v>23.52818629632697</v>
+        <v>23.88741355943234</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.929585842788936</v>
+        <v>1.43508934163686</v>
       </c>
       <c r="C14" t="n">
-        <v>8.283810413847821</v>
+        <v>8.624849931349079</v>
       </c>
       <c r="D14" t="n">
-        <v>6.245005138961428</v>
+        <v>6.805229648912827</v>
       </c>
       <c r="E14" t="n">
-        <v>16.45840139559818</v>
+        <v>16.86516892189877</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.993585975628786</v>
+        <v>1.449913731970987</v>
       </c>
       <c r="C15" t="n">
-        <v>8.911441721172807</v>
+        <v>9.410984405524712</v>
       </c>
       <c r="D15" t="n">
-        <v>6.277638432650592</v>
+        <v>6.860119163057266</v>
       </c>
       <c r="E15" t="n">
-        <v>17.18266612945218</v>
+        <v>17.72101730055297</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.333172506527758</v>
+        <v>1.659615041598106</v>
       </c>
       <c r="C16" t="n">
-        <v>10.51170029657215</v>
+        <v>11.14187433045113</v>
       </c>
       <c r="D16" t="n">
-        <v>6.786566625055096</v>
+        <v>7.344346583222922</v>
       </c>
       <c r="E16" t="n">
-        <v>19.63143942815501</v>
+        <v>20.14583595527216</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.881303490694078</v>
+        <v>1.315031414884518</v>
       </c>
       <c r="C17" t="n">
-        <v>9.722227880202079</v>
+        <v>10.31705899672818</v>
       </c>
       <c r="D17" t="n">
-        <v>6.305569154836414</v>
+        <v>6.831697567019322</v>
       </c>
       <c r="E17" t="n">
-        <v>17.90910052573257</v>
+        <v>18.46378797863202</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.157213865495601</v>
+        <v>1.484009829739479</v>
       </c>
       <c r="C18" t="n">
-        <v>11.35558117071158</v>
+        <v>12.03070943196803</v>
       </c>
       <c r="D18" t="n">
-        <v>6.719169645158552</v>
+        <v>7.312243433294051</v>
       </c>
       <c r="E18" t="n">
-        <v>20.23196468136574</v>
+        <v>20.82696269500156</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.173285075414122</v>
+        <v>1.475311545079852</v>
       </c>
       <c r="C19" t="n">
-        <v>12.17388751715538</v>
+        <v>12.85531859867309</v>
       </c>
       <c r="D19" t="n">
-        <v>6.847562609919951</v>
+        <v>7.421050531355725</v>
       </c>
       <c r="E19" t="n">
-        <v>21.19473520248946</v>
+        <v>21.75168067510867</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.43835695556076</v>
+        <v>1.627148645018664</v>
       </c>
       <c r="C20" t="n">
-        <v>13.96841432827109</v>
+        <v>14.71418915432513</v>
       </c>
       <c r="D20" t="n">
-        <v>7.305852255739404</v>
+        <v>7.875737163100593</v>
       </c>
       <c r="E20" t="n">
-        <v>23.71262353957125</v>
+        <v>24.21707496244439</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.457836435944259</v>
+        <v>0.9621323851159592</v>
       </c>
       <c r="C21" t="n">
-        <v>10.25948931135115</v>
+        <v>10.73842511139091</v>
       </c>
       <c r="D21" t="n">
-        <v>6.105862036838528</v>
+        <v>6.563925880686004</v>
       </c>
       <c r="E21" t="n">
-        <v>17.82318778413393</v>
+        <v>18.26448337719287</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_1_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25003621714446</v>
+        <v>1.254807510987099</v>
       </c>
       <c r="C3" t="n">
-        <v>4.609430044457376</v>
+        <v>4.624077720204738</v>
       </c>
       <c r="D3" t="n">
-        <v>6.213289873310375</v>
+        <v>6.073273015730695</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07275613491221</v>
+        <v>11.95215824692253</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.36463416326243</v>
+        <v>1.387097589754599</v>
       </c>
       <c r="C4" t="n">
-        <v>5.071690741739325</v>
+        <v>5.095714350144471</v>
       </c>
       <c r="D4" t="n">
-        <v>6.623570512313348</v>
+        <v>6.283907873830164</v>
       </c>
       <c r="E4" t="n">
-        <v>13.0598954173151</v>
+        <v>12.76671981372923</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.526670896276484</v>
+        <v>1.562574248815565</v>
       </c>
       <c r="C5" t="n">
-        <v>5.661734659085555</v>
+        <v>5.674900959541969</v>
       </c>
       <c r="D5" t="n">
-        <v>7.059443235250279</v>
+        <v>6.548313004362832</v>
       </c>
       <c r="E5" t="n">
-        <v>14.24784879061232</v>
+        <v>13.78578821272037</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.710738983813212</v>
+        <v>1.756507822737122</v>
       </c>
       <c r="C6" t="n">
-        <v>6.39714752470359</v>
+        <v>6.34125320621215</v>
       </c>
       <c r="D6" t="n">
-        <v>7.498702950836869</v>
+        <v>6.841011655803878</v>
       </c>
       <c r="E6" t="n">
-        <v>15.60658945935367</v>
+        <v>14.93877268475315</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.910364060536848</v>
+        <v>1.969279440336396</v>
       </c>
       <c r="C7" t="n">
-        <v>7.295604067845376</v>
+        <v>7.126966819311608</v>
       </c>
       <c r="D7" t="n">
-        <v>7.919219048187372</v>
+        <v>7.229254080713869</v>
       </c>
       <c r="E7" t="n">
-        <v>17.1251871765696</v>
+        <v>16.32550034036187</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.131284224143347</v>
+        <v>1.17894795474101</v>
       </c>
       <c r="C8" t="n">
-        <v>5.030943853070781</v>
+        <v>4.731971896365897</v>
       </c>
       <c r="D8" t="n">
-        <v>6.184224309267178</v>
+        <v>5.482223884526434</v>
       </c>
       <c r="E8" t="n">
-        <v>12.3464523864813</v>
+        <v>11.39314373563334</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.393508851268624</v>
+        <v>1.46340299349457</v>
       </c>
       <c r="C9" t="n">
-        <v>6.22290430521463</v>
+        <v>5.742753341660136</v>
       </c>
       <c r="D9" t="n">
-        <v>6.73624944889241</v>
+        <v>5.953327938088528</v>
       </c>
       <c r="E9" t="n">
-        <v>14.35266260537566</v>
+        <v>13.15948427324323</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.665334522086016</v>
+        <v>1.762268096505452</v>
       </c>
       <c r="C10" t="n">
-        <v>7.591175547608043</v>
+        <v>6.936007464134947</v>
       </c>
       <c r="D10" t="n">
-        <v>7.2898780799112</v>
+        <v>6.472546319326011</v>
       </c>
       <c r="E10" t="n">
-        <v>16.54638814960526</v>
+        <v>15.17082187996641</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.93805791494681</v>
+        <v>2.075502060244509</v>
       </c>
       <c r="C11" t="n">
-        <v>9.119656841277614</v>
+        <v>8.250512460102451</v>
       </c>
       <c r="D11" t="n">
-        <v>7.950153228552725</v>
+        <v>6.99871756058398</v>
       </c>
       <c r="E11" t="n">
-        <v>19.00786798477715</v>
+        <v>17.32473208093094</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.212493965901895</v>
+        <v>2.391617164613901</v>
       </c>
       <c r="C12" t="n">
-        <v>10.70911728355624</v>
+        <v>9.687482929113896</v>
       </c>
       <c r="D12" t="n">
-        <v>8.514975260105972</v>
+        <v>7.459345122125287</v>
       </c>
       <c r="E12" t="n">
-        <v>21.43658650956411</v>
+        <v>19.53844521585308</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.47154541766642</v>
+        <v>2.707320952149638</v>
       </c>
       <c r="C13" t="n">
-        <v>12.3523616902932</v>
+        <v>11.17278293022815</v>
       </c>
       <c r="D13" t="n">
-        <v>9.063506451472721</v>
+        <v>7.983490017500135</v>
       </c>
       <c r="E13" t="n">
-        <v>23.88741355943234</v>
+        <v>21.86359389987793</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.43508934163686</v>
+        <v>1.583568864427148</v>
       </c>
       <c r="C14" t="n">
-        <v>8.624849931349079</v>
+        <v>7.890738268021484</v>
       </c>
       <c r="D14" t="n">
-        <v>6.805229648912827</v>
+        <v>6.096368536538461</v>
       </c>
       <c r="E14" t="n">
-        <v>16.86516892189877</v>
+        <v>15.57067566898709</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.449913731970987</v>
+        <v>1.616280697932651</v>
       </c>
       <c r="C15" t="n">
-        <v>9.410984405524712</v>
+        <v>8.515070903060199</v>
       </c>
       <c r="D15" t="n">
-        <v>6.860119163057266</v>
+        <v>6.127902272798869</v>
       </c>
       <c r="E15" t="n">
-        <v>17.72101730055297</v>
+        <v>16.25925387379172</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.659615041598106</v>
+        <v>1.871849260302181</v>
       </c>
       <c r="C16" t="n">
-        <v>11.14187433045113</v>
+        <v>10.08285326440306</v>
       </c>
       <c r="D16" t="n">
-        <v>7.344346583222922</v>
+        <v>6.602803089774177</v>
       </c>
       <c r="E16" t="n">
-        <v>20.14583595527216</v>
+        <v>18.55750561447942</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.315031414884518</v>
+        <v>1.494220005863646</v>
       </c>
       <c r="C17" t="n">
-        <v>10.31705899672818</v>
+        <v>9.34065199999247</v>
       </c>
       <c r="D17" t="n">
-        <v>6.831697567019322</v>
+        <v>6.143109544737651</v>
       </c>
       <c r="E17" t="n">
-        <v>18.46378797863202</v>
+        <v>16.97798155059377</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.484009829739479</v>
+        <v>1.709183483185527</v>
       </c>
       <c r="C18" t="n">
-        <v>12.03070943196803</v>
+        <v>10.94212794254508</v>
       </c>
       <c r="D18" t="n">
-        <v>7.312243433294051</v>
+        <v>6.54724598719085</v>
       </c>
       <c r="E18" t="n">
-        <v>20.82696269500156</v>
+        <v>19.19855741292146</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.475311545079852</v>
+        <v>1.719207127245887</v>
       </c>
       <c r="C19" t="n">
-        <v>12.85531859867309</v>
+        <v>11.75833334890179</v>
       </c>
       <c r="D19" t="n">
-        <v>7.421050531355725</v>
+        <v>6.642357704778283</v>
       </c>
       <c r="E19" t="n">
-        <v>21.75168067510867</v>
+        <v>20.11989818092596</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.627148645018664</v>
+        <v>1.926031916099563</v>
       </c>
       <c r="C20" t="n">
-        <v>14.71418915432513</v>
+        <v>13.55689514308195</v>
       </c>
       <c r="D20" t="n">
-        <v>7.875737163100593</v>
+        <v>7.113410070752945</v>
       </c>
       <c r="E20" t="n">
-        <v>24.21707496244439</v>
+        <v>22.59633712993446</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9621323851159592</v>
+        <v>1.156410438309361</v>
       </c>
       <c r="C21" t="n">
-        <v>10.73842511139091</v>
+        <v>9.996135489686939</v>
       </c>
       <c r="D21" t="n">
-        <v>6.563925880686004</v>
+        <v>5.936913074414695</v>
       </c>
       <c r="E21" t="n">
-        <v>18.26448337719287</v>
+        <v>17.08945900241099</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_1_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.254807510987099</v>
+        <v>2.607354527253336</v>
       </c>
       <c r="C3" t="n">
-        <v>4.624077720204738</v>
+        <v>7.722100634219515</v>
       </c>
       <c r="D3" t="n">
-        <v>6.073273015730695</v>
+        <v>8.209499735170802</v>
       </c>
       <c r="E3" t="n">
-        <v>11.95215824692253</v>
+        <v>18.53895489664365</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.387097589754599</v>
+        <v>1.109822166750366</v>
       </c>
       <c r="C4" t="n">
-        <v>5.095714350144471</v>
+        <v>4.537370158074618</v>
       </c>
       <c r="D4" t="n">
-        <v>6.283907873830164</v>
+        <v>5.776770099365121</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76671981372923</v>
+        <v>11.4239624241901</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.562574248815565</v>
+        <v>1.239158535235037</v>
       </c>
       <c r="C5" t="n">
-        <v>5.674900959541969</v>
+        <v>5.233381107181905</v>
       </c>
       <c r="D5" t="n">
-        <v>6.548313004362832</v>
+        <v>6.076615948219984</v>
       </c>
       <c r="E5" t="n">
-        <v>13.78578821272037</v>
+        <v>12.54915559063692</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.756507822737122</v>
+        <v>1.381911531119362</v>
       </c>
       <c r="C6" t="n">
-        <v>6.34125320621215</v>
+        <v>6.126106430539592</v>
       </c>
       <c r="D6" t="n">
-        <v>6.841011655803878</v>
+        <v>6.382308041242458</v>
       </c>
       <c r="E6" t="n">
-        <v>14.93877268475315</v>
+        <v>13.89032600290141</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.969279440336396</v>
+        <v>1.520625513377633</v>
       </c>
       <c r="C7" t="n">
-        <v>7.126966819311608</v>
+        <v>7.163886447658587</v>
       </c>
       <c r="D7" t="n">
-        <v>7.229254080713869</v>
+        <v>6.715410363530768</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32550034036187</v>
+        <v>15.39992232456699</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.17894795474101</v>
+        <v>1.672561635973772</v>
       </c>
       <c r="C8" t="n">
-        <v>4.731971896365897</v>
+        <v>8.33874325458382</v>
       </c>
       <c r="D8" t="n">
-        <v>5.482223884526434</v>
+        <v>7.05080826393081</v>
       </c>
       <c r="E8" t="n">
-        <v>11.39314373563334</v>
+        <v>17.0621131544884</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.46340299349457</v>
+        <v>1.812073945048425</v>
       </c>
       <c r="C9" t="n">
-        <v>5.742753341660136</v>
+        <v>9.63242059608929</v>
       </c>
       <c r="D9" t="n">
-        <v>5.953327938088528</v>
+        <v>7.481073613235315</v>
       </c>
       <c r="E9" t="n">
-        <v>13.15948427324323</v>
+        <v>18.92556815437303</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.762268096505452</v>
+        <v>1.120566829627309</v>
       </c>
       <c r="C10" t="n">
-        <v>6.936007464134947</v>
+        <v>7.03936665889865</v>
       </c>
       <c r="D10" t="n">
-        <v>6.472546319326011</v>
+        <v>5.88347654687254</v>
       </c>
       <c r="E10" t="n">
-        <v>15.17082187996641</v>
+        <v>14.0434100353985</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.075502060244509</v>
+        <v>1.060513322558532</v>
       </c>
       <c r="C11" t="n">
-        <v>8.250512460102451</v>
+        <v>7.502466868468913</v>
       </c>
       <c r="D11" t="n">
-        <v>6.99871756058398</v>
+        <v>5.73037299239525</v>
       </c>
       <c r="E11" t="n">
-        <v>17.32473208093094</v>
+        <v>14.29335318342269</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.391617164613901</v>
+        <v>1.153818624370149</v>
       </c>
       <c r="C12" t="n">
-        <v>9.687482929113896</v>
+        <v>8.890697392182073</v>
       </c>
       <c r="D12" t="n">
-        <v>7.459345122125287</v>
+        <v>6.092127386456115</v>
       </c>
       <c r="E12" t="n">
-        <v>19.53844521585308</v>
+        <v>16.13664340300834</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.707320952149638</v>
+        <v>0.9108851549542757</v>
       </c>
       <c r="C13" t="n">
-        <v>11.17278293022815</v>
+        <v>8.479129119607725</v>
       </c>
       <c r="D13" t="n">
-        <v>7.983490017500135</v>
+        <v>5.546059678399955</v>
       </c>
       <c r="E13" t="n">
-        <v>21.86359389987793</v>
+        <v>14.93607395296196</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.583568864427148</v>
+        <v>0.9906619734013715</v>
       </c>
       <c r="C14" t="n">
-        <v>7.890738268021484</v>
+        <v>9.938978138345689</v>
       </c>
       <c r="D14" t="n">
-        <v>6.096368536538461</v>
+        <v>5.88029568431078</v>
       </c>
       <c r="E14" t="n">
-        <v>15.57067566898709</v>
+        <v>16.80993579605784</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.616280697932651</v>
+        <v>0.9650187233664448</v>
       </c>
       <c r="C15" t="n">
-        <v>8.515070903060199</v>
+        <v>10.73542096341591</v>
       </c>
       <c r="D15" t="n">
-        <v>6.127902272798869</v>
+        <v>5.923414043481301</v>
       </c>
       <c r="E15" t="n">
-        <v>16.25925387379172</v>
+        <v>17.62385373026366</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.871849260302181</v>
+        <v>1.055751846192935</v>
       </c>
       <c r="C16" t="n">
-        <v>10.08285326440306</v>
+        <v>12.60881156761376</v>
       </c>
       <c r="D16" t="n">
-        <v>6.602803089774177</v>
+        <v>6.360537208797194</v>
       </c>
       <c r="E16" t="n">
-        <v>18.55750561447942</v>
+        <v>20.02510062260389</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.494220005863646</v>
+        <v>0.6307827174556182</v>
       </c>
       <c r="C17" t="n">
-        <v>9.34065199999247</v>
+        <v>9.522157515553621</v>
       </c>
       <c r="D17" t="n">
-        <v>6.143109544737651</v>
+        <v>5.291296149147906</v>
       </c>
       <c r="E17" t="n">
-        <v>16.97798155059377</v>
+        <v>15.44423638215715</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.709183483185527</v>
+        <v>0.4938289127131881</v>
       </c>
       <c r="C18" t="n">
-        <v>10.94212794254508</v>
+        <v>8.612342465596974</v>
       </c>
       <c r="D18" t="n">
-        <v>6.54724598719085</v>
+        <v>4.818250835333624</v>
       </c>
       <c r="E18" t="n">
-        <v>19.19855741292146</v>
+        <v>13.92442221364379</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.719207127245887</v>
+        <v>0.5752747022575035</v>
       </c>
       <c r="C19" t="n">
-        <v>11.75833334890179</v>
+        <v>10.76264482725468</v>
       </c>
       <c r="D19" t="n">
-        <v>6.642357704778283</v>
+        <v>5.275784535420808</v>
       </c>
       <c r="E19" t="n">
-        <v>20.11989818092596</v>
+        <v>16.61370406493299</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.926031916099563</v>
+        <v>0.6562492529037804</v>
       </c>
       <c r="C20" t="n">
-        <v>13.55689514308195</v>
+        <v>13.09420726754747</v>
       </c>
       <c r="D20" t="n">
-        <v>7.113410070752945</v>
+        <v>5.768013199376074</v>
       </c>
       <c r="E20" t="n">
-        <v>22.59633712993446</v>
+        <v>19.51846971982732</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.156410438309361</v>
+        <v>0.7309897056280902</v>
       </c>
       <c r="C21" t="n">
-        <v>9.996135489686939</v>
+        <v>15.38555732187431</v>
       </c>
       <c r="D21" t="n">
-        <v>5.936913074414695</v>
+        <v>6.23387211999527</v>
       </c>
       <c r="E21" t="n">
-        <v>17.08945900241099</v>
+        <v>22.35041914749767</v>
       </c>
     </row>
   </sheetData>
